--- a/Re-Imagination/testdata/LC_TestScenarios_new.xlsx
+++ b/Re-Imagination/testdata/LC_TestScenarios_new.xlsx
@@ -3,38 +3,29 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Re-Imagination\Re-Imagination\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7956383-9752-4CD3-8C76-41512127F4CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B1E65A9-6299-4E3C-9308-BF05661F2858}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{ECE7E947-2FB2-45C6-930C-8C5A65B69B33}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="181029" iterateDelta="1E-4"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="51">
   <si>
     <t>Product Type</t>
   </si>
@@ -136,12 +127,64 @@
   </si>
   <si>
     <t>Housing Loan</t>
+  </si>
+  <si>
+    <t>Demat &amp; Trading</t>
+  </si>
+  <si>
+    <t>SBI Home&amp;Top Up Term Loan</t>
+  </si>
+  <si>
+    <t>Motor Private car</t>
+  </si>
+  <si>
+    <t>SBI Life - Saral Shield</t>
+  </si>
+  <si>
+    <t>4088118</t>
+  </si>
+  <si>
+    <t>4088119</t>
+  </si>
+  <si>
+    <t>Deposits</t>
+  </si>
+  <si>
+    <t>Govt Schemes</t>
+  </si>
+  <si>
+    <t>SCSS</t>
+  </si>
+  <si>
+    <t>NPS</t>
+  </si>
+  <si>
+    <t>PPF</t>
+  </si>
+  <si>
+    <t>Sukanya Samriddhi Yojna</t>
+  </si>
+  <si>
+    <t>NPS/APY</t>
+  </si>
+  <si>
+    <t>4089083</t>
+  </si>
+  <si>
+    <t>4089307</t>
+  </si>
+  <si>
+    <t>4089335</t>
+  </si>
+  <si>
+    <t>4089338</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -220,7 +263,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -232,6 +275,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -548,18 +595,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54AF6F5F-47E3-461A-8969-AD96E2E12D36}">
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.33203125" customWidth="1"/>
-    <col min="2" max="2" width="28.6640625" customWidth="1"/>
-    <col min="3" max="3" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25" customWidth="1"/>
-    <col min="6" max="6" width="41.88671875" customWidth="1"/>
-    <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.77734375" customWidth="1"/>
-    <col min="9" max="9" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="7.33203125"/>
+    <col min="2" max="2" customWidth="true" width="28.6640625"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="11.88671875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="21.109375"/>
+    <col min="5" max="5" customWidth="true" width="25.0"/>
+    <col min="6" max="6" customWidth="true" width="41.88671875"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="13.109375"/>
+    <col min="8" max="8" customWidth="true" width="15.77734375"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="17.88671875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
@@ -638,7 +685,9 @@
       <c r="G3" s="4">
         <v>91</v>
       </c>
-      <c r="H3" s="4"/>
+      <c r="H3" t="s" s="0">
+        <v>49</v>
+      </c>
       <c r="I3" s="4"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -652,18 +701,20 @@
         <v>100043</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E4" s="4">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G4" s="4">
-        <v>145</v>
-      </c>
-      <c r="H4" s="4"/>
+        <v>113791</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>50</v>
+      </c>
       <c r="I4" s="4"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -677,16 +728,16 @@
         <v>100043</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E5" s="4">
+        <v>36</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>23</v>
-      </c>
       <c r="G5" s="4">
-        <v>113791</v>
+        <v>145</v>
       </c>
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
@@ -738,7 +789,9 @@
       <c r="G7" s="4">
         <v>279</v>
       </c>
-      <c r="H7" s="4"/>
+      <c r="H7" s="5" t="s">
+        <v>39</v>
+      </c>
       <c r="I7" s="4"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -827,16 +880,16 @@
         <v>200588</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E11" s="4">
-        <v>1113986</v>
+        <v>1113988</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="G11" s="4">
-        <v>100220</v>
+        <v>100229</v>
       </c>
       <c r="H11" s="4"/>
       <c r="I11" s="4"/>
@@ -877,16 +930,16 @@
         <v>200588</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E13" s="4">
-        <v>1113987</v>
+        <v>1113989</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="G13" s="4">
-        <v>100150</v>
+        <v>110198</v>
       </c>
       <c r="H13" s="4"/>
       <c r="I13" s="4"/>
@@ -896,22 +949,22 @@
         <v>14</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="C14" s="4">
-        <v>100075</v>
+        <v>200588</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E14" s="4">
-        <v>306</v>
+        <v>1113986</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G14" s="4">
-        <v>313</v>
+        <v>100220</v>
       </c>
       <c r="H14" s="4"/>
       <c r="I14" s="4"/>
@@ -921,25 +974,227 @@
         <v>15</v>
       </c>
       <c r="B15" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="4">
+        <v>200588</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="4">
+        <v>1113986</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G15" s="4">
+        <v>100221</v>
+      </c>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <v>16</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="4">
+        <v>200588</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E16" s="4">
+        <v>1113987</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G16" s="4">
+        <v>100150</v>
+      </c>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <v>17</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="4">
+        <v>100075</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="4">
+        <v>306</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" s="4">
+        <v>313</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="I17" s="4"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <v>18</v>
+      </c>
+      <c r="B18" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="4">
+      <c r="C18" s="4">
         <v>100037</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D18" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E15" s="4">
+      <c r="E18" s="4">
         <v>5</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F18" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G15" s="4">
+      <c r="G18" s="4">
         <v>92</v>
       </c>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
+        <v>19</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" s="4">
+        <v>100037</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E19" s="4">
+        <v>5</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G19" s="4">
+        <v>135</v>
+      </c>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <v>20</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" s="6">
+        <v>100022</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E20" s="6">
+        <v>76</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="G20" s="6">
+        <v>1115351</v>
+      </c>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <v>21</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" s="6">
+        <v>100022</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E21" s="6">
+        <v>76</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="G21" s="6">
+        <v>78</v>
+      </c>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <v>22</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" s="6">
+        <v>100022</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E22" s="6">
+        <v>76</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G22" s="6">
+        <v>77</v>
+      </c>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <v>23</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" s="6">
+        <v>200543</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E23" s="6">
+        <v>76</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="G23" s="6">
+        <v>113790</v>
+      </c>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -947,19 +1202,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="da1b8369-79b4-4678-ba74-834468944966" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <CreatedDate xmlns="b1d9111c-eb47-4075-a87e-f67550b406dd" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b1d9111c-eb47-4075-a87e-f67550b406dd">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Time xmlns="b1d9111c-eb47-4075-a87e-f67550b406dd" xsi:nil="true"/>
-    <ANNEXURE_records xmlns="b1d9111c-eb47-4075-a87e-f67550b406dd" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1261,22 +1509,25 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="da1b8369-79b4-4678-ba74-834468944966" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <CreatedDate xmlns="b1d9111c-eb47-4075-a87e-f67550b406dd" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b1d9111c-eb47-4075-a87e-f67550b406dd">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <Time xmlns="b1d9111c-eb47-4075-a87e-f67550b406dd" xsi:nil="true"/>
+    <ANNEXURE_records xmlns="b1d9111c-eb47-4075-a87e-f67550b406dd" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{42DE7A88-D326-44CB-B714-BD76A569B38B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD2A4618-A45B-47A4-B143-A1EB0932B33B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="da1b8369-79b4-4678-ba74-834468944966"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="b1d9111c-eb47-4075-a87e-f67550b406dd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1302,9 +1553,13 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD2A4618-A45B-47A4-B143-A1EB0932B33B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{42DE7A88-D326-44CB-B714-BD76A569B38B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="da1b8369-79b4-4678-ba74-834468944966"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="b1d9111c-eb47-4075-a87e-f67550b406dd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>